--- a/tables/table_BacillusCereus.xlsx
+++ b/tables/table_BacillusCereus.xlsx
@@ -429,7 +429,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>整理状況 &lt;br&gt; (文献ファイル名)</t>
+          <t>整理状況</t>
         </is>
       </c>
     </row>
